--- a/final_scores_W.xlsx
+++ b/final_scores_W.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,275 +424,164 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>あいす</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>오칠십일</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>띠기모앙(3)</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>늘코얌</t>
+          <t>ㅇㅇ(1)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>메우메우기여어</t>
+          <t>이하정</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>あやせ_ことり</t>
+          <t>ㅍㅍ</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>제림로</t>
+          <t>아겐티아</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>좆냥이</t>
+          <t>셰리쨩귀여워사랑해잘했어대단해천재야♡</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>키테라</t>
+          <t>리틀륨</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ㅍㅍ(1)</t>
+          <t>띠기모앙(1)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>체늬</t>
+          <t>리타</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.32</v>
+        <v>5.720000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>107.98</v>
+        <v>3.32</v>
       </c>
       <c r="D2" t="n">
-        <v>5.46</v>
+        <v>6.840000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>24.9</v>
+        <v>5.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.840000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>78.54000000000001</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>47.24</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="J2" t="n">
-        <v>14.78</v>
+        <v>0.18</v>
       </c>
       <c r="K2" t="n">
-        <v>6.800000000000001</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>168.12</v>
+        <v>190.26</v>
       </c>
       <c r="C3" t="n">
-        <v>353.58</v>
+        <v>142.94</v>
       </c>
       <c r="D3" t="n">
-        <v>53.66</v>
+        <v>124.38</v>
       </c>
       <c r="E3" t="n">
-        <v>64.23999999999999</v>
+        <v>112.44</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>97.98</v>
       </c>
       <c r="G3" t="n">
-        <v>297.44</v>
+        <v>99.22000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>154.64</v>
+        <v>99.02000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>77.46000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>59.72000000000001</v>
+        <v>72.60000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>156.98</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310.54</v>
+        <v>220.88</v>
       </c>
       <c r="C4" t="n">
-        <v>441.98</v>
+        <v>161.88</v>
       </c>
       <c r="D4" t="n">
-        <v>118.58</v>
+        <v>126.62</v>
       </c>
       <c r="E4" t="n">
-        <v>152.2</v>
+        <v>120.38</v>
       </c>
       <c r="F4" t="n">
-        <v>88.84</v>
+        <v>105.58</v>
       </c>
       <c r="G4" t="n">
-        <v>364.42</v>
+        <v>99.78000000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>217.36</v>
+        <v>99.02000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>213.14</v>
+        <v>77.46000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>116.18</v>
+        <v>73.16000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>281.36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>468.66</v>
-      </c>
-      <c r="C5" t="n">
-        <v>478.34</v>
-      </c>
-      <c r="D5" t="n">
-        <v>257.26</v>
-      </c>
-      <c r="E5" t="n">
-        <v>266.72</v>
-      </c>
-      <c r="F5" t="n">
-        <v>275.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>364.42</v>
-      </c>
-      <c r="H5" t="n">
-        <v>258.22</v>
-      </c>
-      <c r="I5" t="n">
-        <v>282.62</v>
-      </c>
-      <c r="J5" t="n">
-        <v>200.92</v>
-      </c>
-      <c r="K5" t="n">
-        <v>282.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>614.04</v>
-      </c>
-      <c r="C6" t="n">
-        <v>478.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>359.72</v>
-      </c>
-      <c r="E6" t="n">
-        <v>379.28</v>
-      </c>
-      <c r="F6" t="n">
-        <v>384.38</v>
-      </c>
-      <c r="G6" t="n">
-        <v>374.98</v>
-      </c>
-      <c r="H6" t="n">
-        <v>347.4400000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>347.16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>257.98</v>
-      </c>
-      <c r="K6" t="n">
-        <v>282.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>650.14</v>
-      </c>
-      <c r="C7" t="n">
-        <v>478.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>436.14</v>
-      </c>
-      <c r="E7" t="n">
-        <v>427.36</v>
-      </c>
-      <c r="F7" t="n">
-        <v>397.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>376.62</v>
-      </c>
-      <c r="H7" t="n">
-        <v>367.3000000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>362.16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>289.78</v>
-      </c>
-      <c r="K7" t="n">
-        <v>282.1</v>
+        <v>64.86</v>
       </c>
     </row>
   </sheetData>
